--- a/output/independent-code-review/claude/sample-3/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-3/workpaper.xlsx
@@ -11,7 +11,6 @@
     <sheet name="Attribute Verdicts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence Inventory" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Decision Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
-  </numFmts>
-  <fonts count="16">
+  <numFmts count="0"/>
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,10 +109,6 @@
       <b val="1"/>
       <color rgb="00A17321"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="6">
@@ -216,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -250,11 +243,6 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1420,838 +1408,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="16" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="C1" s="16" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D1" s="16" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="E1" s="16" t="inlineStr">
-        <is>
-          <t>Input tokens</t>
-        </is>
-      </c>
-      <c r="F1" s="16" t="inlineStr">
-        <is>
-          <t>Cache read</t>
-        </is>
-      </c>
-      <c r="G1" s="16" t="inlineStr">
-        <is>
-          <t>Output tokens</t>
-        </is>
-      </c>
-      <c r="H1" s="16" t="inlineStr">
-        <is>
-          <t>Cost USD</t>
-        </is>
-      </c>
-      <c r="I1" s="16" t="inlineStr">
-        <is>
-          <t>Latency (ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:48:14.126718Z</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="n">
-        <v>6675</v>
-      </c>
-      <c r="F2" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="17" t="n">
-        <v>1787</v>
-      </c>
-      <c r="H2" s="21" t="n">
-        <v>0.23415</v>
-      </c>
-      <c r="I2" s="17" t="n">
-        <v>25332</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:48:39.485414Z</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="n">
-        <v>7348</v>
-      </c>
-      <c r="F3" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="17" t="n">
-        <v>1988</v>
-      </c>
-      <c r="H3" s="21" t="n">
-        <v>0.25932</v>
-      </c>
-      <c r="I3" s="17" t="n">
-        <v>25349</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:00.506620Z</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>7300</v>
-      </c>
-      <c r="F4" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>1515</v>
-      </c>
-      <c r="H4" s="21" t="n">
-        <v>0.223125</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>21014</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:13.305737Z</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-1</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>6270</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>1005</v>
-      </c>
-      <c r="H5" s="21" t="n">
-        <v>0.119934</v>
-      </c>
-      <c r="I5" s="17" t="n">
-        <v>12795</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:26.208418Z</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-1</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>6246</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <v>1092</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>0.126099</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>12900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:45.900071Z</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-1</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>8041</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>1578</v>
-      </c>
-      <c r="H7" s="21" t="n">
-        <v>0.189474</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>19689</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:10.052239Z</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>1616</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>0.23016</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>24142</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:31.032351Z</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>7295</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>1504</v>
-      </c>
-      <c r="H9" s="21" t="n">
-        <v>0.222225</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>20969</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:44.382655Z</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-2</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>4057</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <v>1067</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>0.091389</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>13346</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:57.753305Z</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-2</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>4033</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>1108</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>0.09410399999999999</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>13368</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:51:17.209066Z</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-2</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>5828</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>1487</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>0.149454</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>19453</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:51:31.339364Z</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:kubernetes-pr-checks.png</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>4703</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>945</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>0.14142</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>14122</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:52:34.116483Z</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:kubernetes-pr.png</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>4172</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <v>4640</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>0.41058</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>62769</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:52:46.504782Z</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-3</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>6582</v>
-      </c>
-      <c r="F15" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <v>1002</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>0.124389</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>12384</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:04.324724Z</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-3</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>6558</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>1257</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>0.143154</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>17817</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:22.086254Z</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-3</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>8353</v>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G17" s="17" t="n">
-        <v>1369</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>0.178479</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>17758</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:36.065782Z</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:nextjs-pr-checks.png</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>4702</v>
-      </c>
-      <c r="F18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <v>924</v>
-      </c>
-      <c r="H18" s="21" t="n">
-        <v>0.13983</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>13972</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:01.769450Z</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>screenshot:nextjs-pr.png</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>6103</v>
-      </c>
-      <c r="F19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="17" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H19" s="21" t="n">
-        <v>0.227145</v>
-      </c>
-      <c r="I19" s="17" t="n">
-        <v>25696</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:15.073618Z</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-4</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>3730</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G20" s="17" t="n">
-        <v>989</v>
-      </c>
-      <c r="H20" s="21" t="n">
-        <v>0.080634</v>
-      </c>
-      <c r="I20" s="17" t="n">
-        <v>13300</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:26.858373Z</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-4</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>3706</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>902</v>
-      </c>
-      <c r="H21" s="21" t="n">
-        <v>0.073749</v>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>11782</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:43.961668Z</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-4</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>5501</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G22" s="17" t="n">
-        <v>1265</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>0.127899</v>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>17098</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E23" s="22">
-        <f>SUM(E2:E22)</f>
-        <v/>
-      </c>
-      <c r="F23" s="22">
-        <f>SUM(F2:F22)</f>
-        <v/>
-      </c>
-      <c r="G23" s="22">
-        <f>SUM(G2:G22)</f>
-        <v/>
-      </c>
-      <c r="H23" s="23">
-        <f>SUM(H2:H22)</f>
-        <v/>
-      </c>
-      <c r="I23" s="22">
-        <f>SUM(I2:I22)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/independent-code-review/claude/sample-3/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-3/workpaper.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Attribute Verdicts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence Inventory" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Decision Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="15">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
+  </numFmts>
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,6 +112,10 @@
       <b val="1"/>
       <color rgb="00A17321"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="6">
@@ -209,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -243,6 +250,11 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -663,7 +675,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>claude:claude-opus-4-7</t>
+          <t>claude:claude-opus-4-8</t>
         </is>
       </c>
     </row>
@@ -675,7 +687,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:53 UTC</t>
+          <t>03 Jul 2026, 04:20 UTC</t>
         </is>
       </c>
     </row>
@@ -751,7 +763,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Remediate the root cause of the FAIL on “Code Review approvals are performed by independent code reviewers”, then re-submit for testing. Rationale: The PR author is BenTheElder.</t>
+          <t>Remediate the root cause of the FAIL on “Code Review approvals are performed by independent code reviewers”, then re-submit for testing. Rationale: The change author is BenTheElder.</t>
         </is>
       </c>
     </row>
@@ -763,7 +775,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The evidence indicates that "13 checks passed" at merge time, showing CI ran and was green, and the PR is scoped to e2e test code (removing the opencontainers/cgroups dependency).</t>
+          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The PR ("remove opencontainers/cgroups dependency from e2e tests") touches 6 files including test code, and the timeline shows "12 checks passed" at merge, indicating CI ran and passed.</t>
         </is>
       </c>
     </row>
@@ -906,11 +918,11 @@
         </is>
       </c>
       <c r="C2" s="17" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>A pull request record (#139018) exists for the change and the PR shows an APPROVED state (lgtm + approved labels, "[APPROVALNOTIFIER] This PR is APPROVED — approved by: BenTheElder, dims") applied 14 hours ago, prior to the merge which occurred 3 hours ago. The merge was performed via the PR (merge commit cbe5c16 into kubernetes:master), indicating the change was not committed directly to main bypassing review. Approval timestamp (14h ago) precedes merge timestamp (3h ago), satisfying the ordering criterion. Note: independence of the reviewer is a separate attribute and not judged here.</t>
+          <t>A code review record exists: the PR #139018 shows multiple reviewers, an 'lgtm' label added 14 hours ago and 'approved' label added May 13, and APPROVALNOTIFIER comments confirming approval — all preceding the merge that occurred '3 hours ago' with '12 checks passed'. The approval/lgtm timestamps clearly precede the merge, and the Kubernetes Prow tide mechanism gates merge on 'lgtm' + 'approved' labels, satisfying the requirement that review occurred prior to the commit to master. Note: this attribute concerns timing of review vs. merge, not reviewer independence — the independence concern (BenTheElder appearing as an approver) belongs to a separate attribute and is not judged here.</t>
         </is>
       </c>
       <c r="E2" s="17" t="n">
@@ -918,7 +930,7 @@
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
-          <t>Independence of reviewer (dims vs. author BenTheElder) is a separate attribute; not evaluated here.</t>
+          <t>Independence of the approver (BenTheElder listed as an approver while also author) is a separate attribute (4-eyes/independence) and is explicitly out of scope for this timing-of-review attribute; noted but not applied here.</t>
         </is>
       </c>
     </row>
@@ -934,20 +946,19 @@
         </is>
       </c>
       <c r="C3" s="17" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>The PR author is BenTheElder. The first approval notifier states "This pull-request has been approved by: BenTheElder" — i.e., the author self-approved. A second approval was later added by dims (/approve /lgtm) 14 hours before merge, and dims is a different individual from the author, which does satisfy independence on its face. However, the initial APPROVED state was driven by the author himself, and the criterion "The approving reviewer is a different individual than the author" is contradicted by the first approval record. Additionally, natasha40575's Jun 3 review is ambiguous (no explicit Approved badge), so it cannot be relied on as the independent approval. Since one recorded approval on this PR is by the author, this fails the independence attribute even though dims provides a secondary independent approval.</t>
+          <t>The change author is BenTheElder. The k8s-ci-robot APPROVALNOTIFIER states "This pull-request has been approved by: BenTheElder" — i.e., the author self-approved via the Prow/OWNERS mechanism, violating the 4-eyes principle. Although a second approval line lists "BenTheElder, dims" (dims being an independent human who issued /approve and /lgtm), the author's own name appearing as an approver on a merged PR means author self-approval was part of the approval basis, weakening independence. Because the author is credited as an approver, the criterion "the approving reviewer has no authorship role in the change" is contradicted.</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>Considered that dims's independent /approve provides an independent second-eye and could satisfy the attribute in isolation. Rejected as a clean SUCCESS because the recorded approval set explicitly includes the author (BenTheElder), directly contradicting the 'approver ≠ author' criterion for at least one of the approvals — this is a Kubernetes/Prow OWNERS convention where /approve from the author is recorded as an approval, which does not meet the 4-eyes standard.
-Considered whether natasha40575's Jun 3 review could serve as the independent approval — rejected due to ambiguity: no explicit Approved badge is visible and the comment expresses reservations rather than approval.</t>
+          <t>Author self-approval via OWNERS/CODEOWNERS alongside a second human approver (dims) — the four-eyes principle is weakened because the author BenTheElder is credited as an approver in the APPROVALNOTIFIER; rejected as clean SUCCESS because independence of the approval is compromised.</t>
         </is>
       </c>
     </row>
@@ -963,11 +974,11 @@
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>The evidence indicates that "13 checks passed" at merge time, showing CI ran and was green, and the PR is scoped to e2e test code (removing the opencontainers/cgroups dependency). However, no coverage report screenshot or artefact is included in the evidence bundle, so the policy thresholds (≥80% line, ≥70% branch, ≥80% function, ≥60% integration) cannot be verified. The change is arguably a test-only / refactor change (natasha40575's review discusses unit test coverage gaps and a follow-up PR #139453 is being tracked), which could qualify for a documented exception, but no exception is explicitly identified/justified on the PR. A coverage report for merge commit cbe5c16 and/or an explicit exception declaration on the PR would resolve this.</t>
+          <t>The PR ("remove opencontainers/cgroups dependency from e2e tests") touches 6 files including test code, and the timeline shows "12 checks passed" at merge, indicating CI ran and passed. However, no coverage report is present in the evidence — I cannot verify unit ≥80%, branch ≥70%, function ≥80%, or integration ≥60% thresholds. While this change plausibly qualifies as a test-only / dependency-removal exception, the exact files changed are not enumerated in the facts (only "6 files, +189/-89"), so I cannot confirm the change is limited to tests with no production behavioral change. A coverage report screenshot for this run, or a file-listing confirming all changes are under test directories, would resolve this to SUCCESS.</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
@@ -975,7 +986,7 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Refactoring with no behavioral changes / test-only change: PR modifies e2e tests only ('remove opencontainers/cgroups dependency from e2e tests', release-note-none, kind/cleanup label). This could plausibly qualify, but the exception is not explicitly identified or justified on the PR as the policy requires, so it cannot be accepted on its face.</t>
+          <t>Dependency Updates / Refactoring with No Behavioral Changes — the PR removes a dependency from e2e tests, which could qualify, but the evidence does not enumerate the 6 changed files, so I cannot confirm the change is limited to tests with no production behavioral change; exception not confirmed.</t>
         </is>
       </c>
     </row>
@@ -990,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1034,12 +1045,12 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>Timeline — approval notifier entry 14 hours ago</t>
+          <t>Timeline — lgtm/approved labels and APPROVALNOTIFIER comments</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>'[APPROVALNOTIFIER] This PR is APPROVED — This pull-request has been approved by: BenTheElder, dims'; lgtm label added 14 hours ago; dims commented '/approve' '/lgtm' 14 hours ago.</t>
+          <t>'approved' label added on May 13 and 'lgtm' label added 14 hours ago; APPROVALNOTIFIER comment states 'This PR is APPROVED'. These review approval events predate the merge.</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1067,12 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Merge footer — bottom of timeline</t>
+          <t>Merge footer / bottom timeline</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>'kubernetes-prow[bot] merged commit cbe5c16 into kubernetes:master 3 hours ago — 13 checks passed'. Merge occurred after the approval 14 hours ago.</t>
+          <t>kubernetes-prow[bot] 'merged commit cbe5c38 into kubernetes:master 3 hours ago' with '12 checks passed' — merge occurred after the approval/lgtm events (14 hours ago / May 13).</t>
         </is>
       </c>
     </row>
@@ -1073,17 +1084,17 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>kubernetes-pr-checks.png</t>
+          <t>kubernetes-pr.png</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Header merge line and status badge</t>
+          <t>Reviewers side panel</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>Purple 'Merged' badge and header 'kubernetes-prow[bot] merged 1 commit into kubernetes:master from BenTheElder:fix-tests 3 hours ago' confirms change reached main via the PR, not a direct commit.</t>
+          <t>Reviewers listed (ndixita, tallclair, natasha41575, and others) plus 'lgtm' label, evidencing a code review record exists for the change.</t>
         </is>
       </c>
     </row>
@@ -1095,17 +1106,17 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>kubernetes-pr.png</t>
+          <t>kubernetes-pr-checks.png</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Labels row near PR header</t>
+          <t>Merged badge / merge footer</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>Labels include 'approved' and 'lgtm', indicating the PR passed Kubernetes' review gating before merge.</t>
+          <t>Purple 'Merged' badge and footer 'kubernetes-prow[bot] merged 1 commit into kubernetes:master' confirms the change reached the main (master) branch.</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1133,12 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>PR header / opening comment</t>
+          <t>Merge/branch header line</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>PR #139018 authored by BenTheElder (labelled 'Member'), opening comment on May 13.</t>
+          <t>PR authored from BenTheElder:fix-tests; BenTheElder carries 'Author' badge on comments, confirming BenTheElder is the change author.</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1155,12 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Approval notifier comment (first occurrence, May 13)</t>
+          <t>k8s-ci-robot APPROVALNOTIFIER comment</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>kubernetes-prow[bot] posts '[APPROVALNOTIFIER] This PR is APPROVED — This pull-request has been approved by: BenTheElder' — the author himself is listed as the approver.</t>
+          <t>'This PR is APPROVED' — 'This pull-request has been approved by: BenTheElder', i.e., the author is listed as an approver (self-approval).</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1177,12 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>dims comment 14 hours ago and second approval notifier</t>
+          <t>kubernetes-prow[bot] APPROVALNOTIFIER comment and dims comment</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>dims commented '/approve' and '/lgtm'; subsequent APPROVALNOTIFIER lists 'BenTheElder, dims'. dims is a distinct individual from the author.</t>
+          <t>Second approval line reads 'approved by: BenTheElder, dims'; dims issued '/approve' and '/lgtm' — an independent human approver exists, but the author's name still appears in the approver set.</t>
         </is>
       </c>
     </row>
@@ -1188,19 +1199,19 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>natasha40575 review Jun 3 (ambiguity note)</t>
+          <t>Reviewers side panel</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>natasha40575 'reviewed on Jun 3' but no explicit Approved/Changes-requested badge visible; substantive comment raises concerns and suggests waiting for #139453.</t>
+          <t>Lists ndixita, tallclair, natasha41575 and others as reviewers; natasha41575 left a substantive review comment, but the recorded APPROVED attribution includes the author.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Code Review approvals are performed by independent code reviewers</t>
+          <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -1210,12 +1221,12 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Merge line header</t>
+          <t>Timeline near merge event</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>kubernetes-prow[bot] merged 1 commit into master from BenTheElder:fix-tests 3 hours ago (merge commit cbe5c16); bot is the merger, not a human reviewer.</t>
+          <t>kubernetes-prow bot 'merged commit cbe5c38 into kubernetes:master' with '12 checks passed' — CI pipeline ran and passed before merge.</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1243,12 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Merge status line near bottom ('kubernetes-prow[bot] merged commit cbe5c16 ... 13 checks passed')</t>
+          <t>PR title / tab bar</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>PR was merged with '13 checks passed' shown, indicating CI test suites completed successfully prior to merge.</t>
+          <t>Title 'remove opencontainers/cgroups dependency from e2e tests'; tabs show 'Files changed 6' but the individual filenames are not listed, so I cannot confirm the change is exclusively test-only.</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1265,12 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Checks tab panel body</t>
+          <t>Checks tab center panel</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Checks tab shows '0' and panel reads 'Workflow runs completed with no jobs' — no coverage report artefact is visible in the GitHub Actions Checks view (CI likely ran externally via Prow).</t>
+          <t>Displays 'Workflow runs completed with no jobs'; no coverage numbers or per-job coverage detail are visible on this page.</t>
         </is>
       </c>
     </row>
@@ -1276,34 +1287,12 @@
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>PR description 'What this PR does' and natasha40575 review on Jun 3</t>
+          <t>natasha41575 review comment (Jun 3)</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>PR removes opencontainers/cgroups dependency from e2e tests; reviewer discusses unit test coverage gaps and references follow-up PR #139453 for expanded coverage, but no explicit exception label/justification (e.g., 'refactor / test-only exception') is recorded on the PR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>kubernetes-pr.png</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Labels row in sidebar</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Labels include 'kind/cleanup', 'area/test', 'lgtm', 'approved', 'release-note-none' — no exception waiver label is present, and no coverage report is linked in the PR conversation.</t>
+          <t>Reviewer states OK to remove the cgroups dependency 'provided that we have sufficient unit test coverage', with detailed coverage notes — indicating coverage was discussed but no numeric coverage report artifact is captured in the evidence.</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1360,12 @@
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>GitHub Pull Request page — Checks tab · 11 facts extracted · 2 people · 3 ambiguity flag(s)</t>
+          <t>GitHub Pull Request page — "Checks" tab · 13 facts extracted · 2 people · 4 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E2" s="17" t="inlineStr">
         <is>
-          <t>code-review-prior-to-merge, testing-per-policy</t>
+          <t>code-review-before-commit-to-main, testing-per-testing-policy</t>
         </is>
       </c>
     </row>
@@ -1396,13 +1385,847 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>GitHub Pull Request page (kubernetes/kubernetes #139018) · 67 facts extracted · 14 people · 8 ambiguity flag(s)</t>
+          <t>GitHub Pull Request page (kubernetes/kubernetes PR #139018) · 27 facts extracted · 12 people · 7 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>code-review-prior-to-merge, code-review-prior-to-merge, code-review-prior-to-merge, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-policy, testing-per-policy, testing-per-policy</t>
-        </is>
+          <t>code-review-before-commit-to-main, code-review-before-commit-to-main, code-review-before-commit-to-main, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-testing-policy, testing-per-testing-policy, testing-per-testing-policy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>Input tokens</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>Cache read</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>Output tokens</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>Cost USD</t>
+        </is>
+      </c>
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>Latency (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:15:40.084130Z</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>4474</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="17" t="n">
+        <v>1660</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="17" t="n">
+        <v>23603</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:06.122392Z</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>5147</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>2338</v>
+      </c>
+      <c r="H3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="17" t="n">
+        <v>26026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:30.394765Z</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>5099</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>1763</v>
+      </c>
+      <c r="H4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>24264</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:44.295721Z</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-1</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>6383</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>13897</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:55.782597Z</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-1</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>6355</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>927</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>11484</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:11.438826Z</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-1</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>8116</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>1317</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>15655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:34.006071Z</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>5063</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>1746</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>22559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:57.834234Z</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>5094</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>1921</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>23819</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:09.107798Z</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-2</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>4233</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>946</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>11269</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:20.213919Z</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-2</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>4205</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>943</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>11102</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:39.404920Z</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-2</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>1616</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>19186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:52.612761Z</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>2502</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>963</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>13198</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:22.610986Z</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr.png</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>1971</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>2247</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>29989</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:35.659572Z</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-3</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>3818</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>13044</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:48.832139Z</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-3</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>3790</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>994</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>13169</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:03.784191Z</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-3</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>5551</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>1256</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>14948</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:18.239343Z</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>2501</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>1103</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>14446</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:41.669803Z</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr.png</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>3902</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>1798</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>23426</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:53.838524Z</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-4</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>3513</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>912</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>12165</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:21:02.663985Z</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-4</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>3485</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>711</v>
+      </c>
+      <c r="H21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>8821</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:21:19.635538Z</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-4</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>5246</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>1284</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>16967</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E23" s="22">
+        <f>SUM(E2:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="22">
+        <f>SUM(F2:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="22">
+        <f>SUM(G2:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="23">
+        <f>SUM(H2:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="22">
+        <f>SUM(I2:I22)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
